--- a/objectifs_commerciaux_2026.xlsx
+++ b/objectifs_commerciaux_2026.xlsx
@@ -436,7 +436,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="3">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7500</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3500</v>
+        <v>2700000</v>
       </c>
     </row>
   </sheetData>
